--- a/Simple_explanation_graph.xlsx
+++ b/Simple_explanation_graph.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dropbox\Root\Github Repositories\Repo_Seismic_Desing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC83FDF3-F7F8-4BD5-91F3-86EEF1442E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A475E47-3DDA-4927-B110-37918B71BE54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{54E10262-5C34-4AD5-87B4-777128C54468}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="28">
   <si>
     <t>K</t>
   </si>
@@ -81,6 +81,48 @@
   </si>
   <si>
     <t>Cumulative Effective Mass [%]</t>
+  </si>
+  <si>
+    <t>qn1</t>
+  </si>
+  <si>
+    <t>qn2</t>
+  </si>
+  <si>
+    <t>qn3</t>
+  </si>
+  <si>
+    <t>Desplazamientos qn</t>
+  </si>
+  <si>
+    <t>Qn1</t>
+  </si>
+  <si>
+    <t>Qn2</t>
+  </si>
+  <si>
+    <t>Qn3</t>
+  </si>
+  <si>
+    <t>Fuerzas Laterales Qn</t>
+  </si>
+  <si>
+    <t>qn_SRSS</t>
+  </si>
+  <si>
+    <t>Qn_SRSS</t>
+  </si>
+  <si>
+    <t>qn_CQC</t>
+  </si>
+  <si>
+    <t>Qn_CQC</t>
+  </si>
+  <si>
+    <t>VSRSS</t>
+  </si>
+  <si>
+    <t>VCQC</t>
   </si>
 </sst>
 </file>
@@ -905,6 +947,714 @@
               </a:solidFill>
             </a:rPr>
             <a:t> = 100</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>458625</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>153876</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0CD8401-0465-4687-B176-CADA1818B821}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3051422" y="3251048"/>
+          <a:ext cx="8392323" cy="3918247"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>211033</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>74147</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>99650</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>143987</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BC50E5B-FC2D-B938-1E10-563B140B27DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5703593" y="6524910"/>
+          <a:ext cx="498901" cy="1199152"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>604582</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>25282</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>461991</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>99932</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{480D3C35-66E6-6CEC-8E59-D3548D98ACAB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4266289" y="6476045"/>
+          <a:ext cx="467693" cy="1203962"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>325106</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>142590</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>180516</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>54306</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAEDE88F-6414-1810-2CC0-57D747920767}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3376528" y="6405135"/>
+          <a:ext cx="465695" cy="1229246"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>179321</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>179321</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>373242</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>65248</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="10" name="TextBox 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C187A6F0-F6AC-48BE-9B3E-C20F1BF8FFC3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7502734" y="1924620"/>
+          <a:ext cx="804206" cy="262365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>F1 = 4.68</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>137799</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>29431</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>331720</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>103577</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDEBF084-87CF-481F-B6B1-6436BE4073F1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7461212" y="1021856"/>
+          <a:ext cx="804206" cy="262365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>F2 = 8.44</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>147609</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>147609</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>341530</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>33537</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05650DF3-9D71-4C31-B09D-149205CD7FA9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7471022" y="387160"/>
+          <a:ext cx="804206" cy="262365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>F3 = 10.52</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>353622</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>148293</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>188219</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>165404</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="Straight Arrow Connector 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{62C3CFF8-065B-557E-4939-402F54D15F99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="7066751" y="3022904"/>
+          <a:ext cx="444881" cy="17111"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>183428</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>69356</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>377350</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>143502</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="TextBox 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C61728C3-0ECA-405E-9FD4-975A72AFBF83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6896557" y="2755748"/>
+          <a:ext cx="804206" cy="262365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>VT1 = 23.64</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>183428</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>137798</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>377349</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>23726</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="TextBox 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E09681AD-A831-4FD7-A877-E10096AA3992}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7506841" y="2071316"/>
+          <a:ext cx="804206" cy="262365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>d1 = 0.089</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>119091</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>56350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>313012</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>130497</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="TextBox 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5EA8D27F-3DD2-4C3D-9BC0-3CACF4C7B93A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7442504" y="1236994"/>
+          <a:ext cx="804206" cy="262365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>d2 = 0.16</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>168827</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>111789</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>362748</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>185935</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="TextBox 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B8468354-62B0-4BE5-A3E0-2D65A415154E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7492240" y="539558"/>
+          <a:ext cx="804206" cy="262365"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="900" b="1">
+              <a:solidFill>
+                <a:srgbClr val="FF0000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>d3 = 0.20</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1231,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DBF9CAA-8CD6-4513-9379-7526EF1B8D10}">
-  <dimension ref="A1:E32"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -1450,8 +2200,225 @@
         <v>100</v>
       </c>
     </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C35" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2">
+        <v>8.9691999999999994E-2</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1.7010999999999998E-2</v>
+      </c>
+      <c r="E36" s="2">
+        <v>2.5089999999999999E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0.16161900000000001</v>
+      </c>
+      <c r="D37" s="2">
+        <v>7.5700000000000003E-3</v>
+      </c>
+      <c r="E37" s="2">
+        <v>-3.1289999999999998E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="2">
+        <v>0.20153599999999999</v>
+      </c>
+      <c r="D38" s="2">
+        <v>-1.3641E-2</v>
+      </c>
+      <c r="E38" s="2">
+        <v>1.392E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B43" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2">
+        <v>4.6840099999999998</v>
+      </c>
+      <c r="D43" s="2">
+        <v>6.9743110000000001</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2.1479379999999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B44" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C44" s="2">
+        <v>8.4402950000000008</v>
+      </c>
+      <c r="D44" s="2">
+        <v>3.1038600000000001</v>
+      </c>
+      <c r="E44" s="2">
+        <v>-2.6784349999999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C45" s="2">
+        <v>10.524875</v>
+      </c>
+      <c r="D45" s="2">
+        <v>-5.5929630000000001</v>
+      </c>
+      <c r="E45" s="2">
+        <v>1.192016</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C48" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C49" s="2">
+        <v>8.9691999999999994E-2</v>
+      </c>
+      <c r="D49" s="2">
+        <v>4.6840099999999998</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0.16161900000000001</v>
+      </c>
+      <c r="D50" s="2">
+        <v>8.4402950000000008</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0.20153599999999999</v>
+      </c>
+      <c r="D51" s="2">
+        <v>10.524875</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="C53" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C54" s="2">
+        <v>9.1325000000000003E-2</v>
+      </c>
+      <c r="D54" s="2">
+        <v>8.6714819999999992</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0.161827</v>
+      </c>
+      <c r="D55" s="2">
+        <v>9.3833120000000001</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C56" s="2">
+        <v>0.20200199999999999</v>
+      </c>
+      <c r="D56" s="2">
+        <v>11.978111</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B58" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C58" s="2">
+        <f>+SUM(D49:D51)</f>
+        <v>23.649180000000001</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="2">
+        <f>+SUM(D54:D56)</f>
+        <v>30.032905</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>